--- a/artfynd/A 51644-2024 artfynd.xlsx
+++ b/artfynd/A 51644-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121506580</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51644-2024 artfynd.xlsx
+++ b/artfynd/A 51644-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121506580</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51644-2024 artfynd.xlsx
+++ b/artfynd/A 51644-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121506580</v>
       </c>
       <c r="B2" t="n">
-        <v>57375</v>
+        <v>57376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
